--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>42</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR ADINOLFI VINCENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
